--- a/VerveStacks_NOR_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_NOR_grids_kan10/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB614A65-B991-4D21-84DF-A2FF913B8BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7A76392-CCCF-40B5-BF68-78F0B9EAB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -1623,7 +1623,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{063C600A-02C0-4762-AD01-A94DF64561CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D500A44-DA6F-4F38-BAC1-D79FA750D506}">
   <dimension ref="B9:E79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
